--- a/counselor_forms/007_discord_report_form--counselor_forms.xlsx
+++ b/counselor_forms/007_discord_report_form--counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_101,_'label':_'spamming',_'name':_'spamming'}</t>
+          <t>spamming</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 101, 'label': 'Spamming', 'name': 'spamming'}</t>
+          <t>Spamming</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_102,_'label':_'trolling',_'name':_'trolling'}</t>
+          <t>trolling</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 102, 'label': 'Trolling', 'name': 'trolling'}</t>
+          <t>Trolling</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_103,_'label':_'harassment',_'name':_'harassment'}</t>
+          <t>harassment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 103, 'label': 'Harassment', 'name': 'harassment'}</t>
+          <t>Harassment</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_104,_'label':_'inappropriate_content',_'name':_'in_appropriate_content'}</t>
+          <t>inappropriate_content</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 104, 'label': 'Inappropriate Content', 'name': 'in_appropriate_content'}</t>
+          <t>Inappropriate Content</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_105,_'label':_'self_promotion',_'name':_'self_promotion'}</t>
+          <t>self_promotion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 105, 'label': 'Self Promotion', 'name': 'self_promotion'}</t>
+          <t>Self Promotion</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_106,_'label':_'none_of_the_above',_'name':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 106, 'label': 'None of the above', 'name': 'none_of_the_above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_201,_'label':_'accept',_'name':_'accept'}</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 201, 'label': 'Accept', 'name': 'accept'}</t>
+          <t>Accept</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_202,_'label':_'reject',_'name':_'reject'}</t>
+          <t>reject</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 202, 'label': 'Reject', 'name': 'reject'}</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_203,_'label':_'hold',_'name':_'hold'}</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 203, 'label': 'Hold', 'name': 'hold'}</t>
+          <t>Hold</t>
         </is>
       </c>
     </row>
